--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803106</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128803065</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96188</v>
+        <v>96215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96215</v>
+        <v>96221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96221</v>
+        <v>96228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803106</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128803065</v>
       </c>
       <c r="B3" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96228</v>
+        <v>96232</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803106</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128803065</v>
       </c>
       <c r="B3" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96232</v>
+        <v>96239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803106</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128803065</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128803106</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128803065</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>128802172</v>
       </c>
       <c r="B4" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 40931-2025 artfynd.xlsx
+++ b/artfynd/A 40931-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,46 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128803106</v>
+        <v>128802172</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334568</v>
+        <v>334577</v>
       </c>
       <c r="R2" t="n">
-        <v>6431804</v>
+        <v>6432026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,43 +752,39 @@
           <t>2025-09-28</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128803065</v>
+        <v>128802057</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,14 +805,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334682</v>
+        <v>334514</v>
       </c>
       <c r="R3" t="n">
-        <v>6431688</v>
+        <v>6431917</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,6 +858,11 @@
           <t>2025-09-28</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack på träd</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -882,22 +875,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128802172</v>
+        <v>128803065</v>
       </c>
       <c r="B4" t="n">
-        <v>96301</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,27 +898,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334577</v>
+        <v>334682</v>
       </c>
       <c r="R4" t="n">
-        <v>6432026</v>
+        <v>6431688</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,22 +974,237 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128803106</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Frövet, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>334568</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6431804</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128802144</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Frövet, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334514</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6431917</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skepplanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
